--- a/business_surveys/013_donor_demographic_research_survey--business_surveys.xlsx
+++ b/business_surveys/013_donor_demographic_research_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>credit_card</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nonprofit_a</t>
+          <t>nonprofit a</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nonprofit_b</t>
+          <t>nonprofit b</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nonprofit_c</t>
+          <t>nonprofit c</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>charity_a</t>
+          <t>charity a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>charity_b</t>
+          <t>charity b</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>charity_c</t>
+          <t>charity c</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>charity_d</t>
+          <t>charity d</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>charity_e</t>
+          <t>charity e</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>charity_f</t>
+          <t>charity f</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>charity_g</t>
+          <t>charity g</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>charity_h</t>
+          <t>charity h</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>charity_i</t>
+          <t>charity i</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>charity_j</t>
+          <t>charity j</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>program_a</t>
+          <t>program a</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>program_b</t>
+          <t>program b</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>program_c</t>
+          <t>program c</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>program_d</t>
+          <t>program d</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>program_e</t>
+          <t>program e</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>program_f</t>
+          <t>program f</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>program_g</t>
+          <t>program g</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>program_h</t>
+          <t>program h</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>program_i</t>
+          <t>program i</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>program_j</t>
+          <t>program j</t>
         </is>
       </c>
     </row>
